--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0003T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0003T0006Z000C1N21_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.44059352104227</v>
+        <v>7.54659644716937</v>
       </c>
       <c r="D2" t="n">
-        <v>46.81794969092672</v>
+        <v>7.607916824775592</v>
       </c>
       <c r="E2" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F2" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>42.69667366917152</v>
+        <v>6.938209471240372</v>
       </c>
       <c r="D3" t="n">
-        <v>42.76409616530407</v>
+        <v>6.949165626861912</v>
       </c>
       <c r="E3" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F3" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>43.08155529544568</v>
+        <v>7.000752735509923</v>
       </c>
       <c r="D4" t="n">
-        <v>43.25010363584765</v>
+        <v>7.028141840825244</v>
       </c>
       <c r="E4" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F4" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>9.885446349929209</v>
+        <v>1.606385031863496</v>
       </c>
       <c r="D5" t="n">
-        <v>10.01581838017891</v>
+        <v>1.627570486779073</v>
       </c>
       <c r="E5" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F5" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.00997213074295</v>
+        <v>2.76412047124573</v>
       </c>
       <c r="D6" t="n">
-        <v>17.10762700444502</v>
+        <v>2.779989388222317</v>
       </c>
       <c r="E6" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F6" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>58.34675197137109</v>
+        <v>9.481347195347803</v>
       </c>
       <c r="D7" t="n">
-        <v>57.82969656725478</v>
+        <v>9.397325692178901</v>
       </c>
       <c r="E7" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F7" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>17.48161282193863</v>
+        <v>2.840762083565028</v>
       </c>
       <c r="D8" t="n">
-        <v>17.61540490112895</v>
+        <v>2.862503296433454</v>
       </c>
       <c r="E8" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F8" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>64.71350668377683</v>
+        <v>10.51594483611374</v>
       </c>
       <c r="D9" t="n">
-        <v>64.10669957081278</v>
+        <v>10.41733868025708</v>
       </c>
       <c r="E9" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F9" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>40.2104881455632</v>
+        <v>6.53420432365402</v>
       </c>
       <c r="D10" t="n">
-        <v>40.32323979388844</v>
+        <v>6.552526466506872</v>
       </c>
       <c r="E10" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F10" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>33.29644986225868</v>
+        <v>5.410673102617036</v>
       </c>
       <c r="D11" t="n">
-        <v>33.17275693794716</v>
+        <v>5.390573002416414</v>
       </c>
       <c r="E11" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F11" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>33.22740387266595</v>
+        <v>5.399453129308216</v>
       </c>
       <c r="D12" t="n">
-        <v>33.74373161621808</v>
+        <v>5.483356387635438</v>
       </c>
       <c r="E12" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F12" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>15.72401696645877</v>
+        <v>2.55515275704955</v>
       </c>
       <c r="D13" t="n">
-        <v>15.8508389877995</v>
+        <v>2.57576133551742</v>
       </c>
       <c r="E13" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F13" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>33.31601705162376</v>
+        <v>5.413852770888862</v>
       </c>
       <c r="D14" t="n">
-        <v>32.90605112621827</v>
+        <v>5.34723330801047</v>
       </c>
       <c r="E14" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F14" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>37.68885171876105</v>
+        <v>6.124438404298671</v>
       </c>
       <c r="D15" t="n">
-        <v>37.14604686345112</v>
+        <v>6.036232615310807</v>
       </c>
       <c r="E15" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F15" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>40.50820195600389</v>
+        <v>6.582582817850633</v>
       </c>
       <c r="D16" t="n">
-        <v>41.48816352853978</v>
+        <v>6.741826573387715</v>
       </c>
       <c r="E16" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F16" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>33.78458492364403</v>
+        <v>5.489995050092156</v>
       </c>
       <c r="D17" t="n">
-        <v>33.06567261093791</v>
+        <v>5.373171799277411</v>
       </c>
       <c r="E17" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F17" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>24.54383586648876</v>
+        <v>3.988373328304423</v>
       </c>
       <c r="D18" t="n">
-        <v>25.52177030611393</v>
+        <v>4.147287674743514</v>
       </c>
       <c r="E18" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F18" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>36.82813385829124</v>
+        <v>5.984571751972326</v>
       </c>
       <c r="D19" t="n">
-        <v>35.95689852789509</v>
+        <v>5.842996010782953</v>
       </c>
       <c r="E19" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F19" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>36.45766617524085</v>
+        <v>5.924370753476637</v>
       </c>
       <c r="D20" t="n">
-        <v>37.37253159337025</v>
+        <v>6.073036383922666</v>
       </c>
       <c r="E20" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F20" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>33.94008505522934</v>
+        <v>5.515263821474768</v>
       </c>
       <c r="D21" t="n">
-        <v>33.02245805706524</v>
+        <v>5.366149434273102</v>
       </c>
       <c r="E21" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F21" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>30.60452895754078</v>
+        <v>4.973235955600376</v>
       </c>
       <c r="D22" t="n">
-        <v>31.36874461587314</v>
+        <v>5.097421000079385</v>
       </c>
       <c r="E22" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F22" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>32.45435935032273</v>
+        <v>5.273833394427444</v>
       </c>
       <c r="D23" t="n">
-        <v>31.47452891920915</v>
+        <v>5.114610949371487</v>
       </c>
       <c r="E23" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F23" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>54.74006554940222</v>
+        <v>8.895260651777861</v>
       </c>
       <c r="D24" t="n">
-        <v>53.76702523465961</v>
+        <v>8.737141600632187</v>
       </c>
       <c r="E24" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F24" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>29.87990644754632</v>
+        <v>4.855484797726278</v>
       </c>
       <c r="D25" t="n">
-        <v>30.14846916394281</v>
+        <v>4.899126239140707</v>
       </c>
       <c r="E25" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F25" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>43.45822055389365</v>
+        <v>7.061960840007719</v>
       </c>
       <c r="D26" t="n">
-        <v>42.50482955806712</v>
+        <v>6.907034803185907</v>
       </c>
       <c r="E26" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F26" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>47.04888500624567</v>
+        <v>7.645443813514921</v>
       </c>
       <c r="D27" t="n">
-        <v>47.60682225591923</v>
+        <v>7.736108616586875</v>
       </c>
       <c r="E27" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F27" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>42.66579701592777</v>
+        <v>6.933192015088262</v>
       </c>
       <c r="D28" t="n">
-        <v>41.80022609040635</v>
+        <v>6.792536739691032</v>
       </c>
       <c r="E28" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F28" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>54.63239044661262</v>
+        <v>8.877763447574551</v>
       </c>
       <c r="D29" t="n">
-        <v>53.70443774132164</v>
+        <v>8.726971132964767</v>
       </c>
       <c r="E29" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F29" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>47.24925937264157</v>
+        <v>7.678004648054255</v>
       </c>
       <c r="D30" t="n">
-        <v>47.51000904575118</v>
+        <v>7.720376469934566</v>
       </c>
       <c r="E30" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F30" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>51.69357596796975</v>
+        <v>8.400206094795085</v>
       </c>
       <c r="D31" t="n">
-        <v>51.13582230299121</v>
+        <v>8.309571124236072</v>
       </c>
       <c r="E31" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F31" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>62.80479687814881</v>
+        <v>10.20577949269918</v>
       </c>
       <c r="D32" t="n">
-        <v>62.00485918410633</v>
+        <v>10.07578961741728</v>
       </c>
       <c r="E32" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F32" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>60.53381632142873</v>
+        <v>9.836745152232169</v>
       </c>
       <c r="D33" t="n">
-        <v>59.92845789124445</v>
+        <v>9.738374407327223</v>
       </c>
       <c r="E33" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F33" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>62.92365170584422</v>
+        <v>10.22509340219969</v>
       </c>
       <c r="D34" t="n">
-        <v>62.7462141297615</v>
+        <v>10.19625979608624</v>
       </c>
       <c r="E34" t="n">
-        <v>13.94758354032405</v>
+        <v>2.266482325302658</v>
       </c>
       <c r="F34" t="n">
-        <v>13.72295998136477</v>
+        <v>2.229980996971776</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
